--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/phi-4/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/phi-4/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D2">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="D3">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="H3">
         <v>426</v>
